--- a/New folder (2)/kutai timur.xlsx
+++ b/New folder (2)/kutai timur.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jati\Documents\GitHub\kutaitimur.github.io\New folder (2)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jati\Documents\GitHub2\kutaitimur.github.io\New folder (2)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA63FBD3-3CDB-4CCD-8B6F-3F71C4A85554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D45F9C-1B50-4AC7-AE62-3646E269028A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="429">
   <si>
     <t>Indomaret AWS Sangatta</t>
   </si>
@@ -979,33 +979,18 @@
     <t>Toko Tiga Dara</t>
   </si>
   <si>
-    <t>3VMV+MV6, Sidomulyo, Kec. Kongbeng, Kabupaten Kutai Timur, Kalimantan Timur 75655</t>
-  </si>
-  <si>
     <t>1.0841723680020638, 116.89464901518055</t>
   </si>
   <si>
     <t>TOKO FADIL JAYA SP1</t>
   </si>
   <si>
-    <t>3VPW+442, Jl. Ahmad Yani, Marga Mulia, Kec. Kongbeng, Kabupaten Kutai Timur, Kalimantan Timur 75655</t>
-  </si>
-  <si>
     <t>1.0852741060509885, 116.89526000407398</t>
   </si>
   <si>
-    <t>Pasar landasan sp 1, Jl. Ahmad Yani desa, wanasari, Kec. Muara Wahau, Kabupaten Kutai Timur, Kalimantan Timur 75655</t>
-  </si>
-  <si>
-    <t>1.0872907489744383, 116.89607733084614</t>
-  </si>
-  <si>
     <t>Kios Mama Sheza</t>
   </si>
   <si>
-    <t>3VPW+XGQ, Wanasari, Kec. Kongbeng, Kabupaten Kutai Timur, Kalimantan Timur 75655</t>
-  </si>
-  <si>
     <t>1.0874791765432796, 116.89639431049123</t>
   </si>
   <si>
@@ -1018,9 +1003,6 @@
     <t>Nadia Magelang Jaya</t>
   </si>
   <si>
-    <t>3VQW+WGM, Jl. Ahmad Yani, Marga Mulia, Kec. Kongbeng, Kabupaten Kutai Timur, Kalimantan Timur 75655</t>
-  </si>
-  <si>
     <t>1.089835520645916, 116.8962890270061</t>
   </si>
   <si>
@@ -1322,6 +1304,12 @@
   </si>
   <si>
     <t>Mulawarman, Sangatta Selatan, Kabupaten Kutai Timur, Kalimantan Timur 75683</t>
+  </si>
+  <si>
+    <t>Jl. Ahmad Yani, Marga Mulia, Kec. Kongbeng, Kabupaten Kutai Timur, Kalimantan Timur 75655</t>
+  </si>
+  <si>
+    <t>Wanasari, Kec. Kongbeng, Kabupaten Kutai Timur, Kalimantan Timur 75655</t>
   </si>
 </sst>
 </file>
@@ -2159,13 +2147,13 @@
     </row>
     <row r="51" spans="2:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B51" s="4" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="D51" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -2357,13 +2345,13 @@
     </row>
     <row r="27" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C27" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="D27" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -2688,7 +2676,7 @@
         <v>273</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="D50" t="s">
         <v>145</v>
@@ -2699,7 +2687,7 @@
         <v>154</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>155</v>
@@ -2881,7 +2869,7 @@
         <v>280</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="D88" t="s">
         <v>281</v>
@@ -2892,7 +2880,7 @@
         <v>285</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D90" t="s">
         <v>286</v>
@@ -2903,7 +2891,7 @@
         <v>287</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="D92" t="s">
         <v>288</v>
@@ -2914,7 +2902,7 @@
         <v>289</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="D94" t="s">
         <v>290</v>
@@ -2939,7 +2927,7 @@
         <v>295</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="D99" t="s">
         <v>294</v>
@@ -2964,7 +2952,7 @@
         <v>299</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="D103" t="s">
         <v>300</v>
@@ -2975,7 +2963,7 @@
         <v>301</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="D105" t="s">
         <v>302</v>
@@ -2986,7 +2974,7 @@
         <v>303</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="D107" t="s">
         <v>304</v>
@@ -3000,7 +2988,7 @@
         <v>305</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="D109" t="s">
         <v>306</v>
@@ -3014,7 +3002,7 @@
         <v>307</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="D111" t="s">
         <v>308</v>
@@ -3025,7 +3013,7 @@
         <v>310</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="D113" t="s">
         <v>309</v>
@@ -3036,7 +3024,7 @@
         <v>311</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="D115" t="s">
         <v>312</v>
@@ -3050,7 +3038,7 @@
         <v>313</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="D117" t="s">
         <v>314</v>
@@ -3061,126 +3049,115 @@
         <v>315</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="D119" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="121" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B121" s="6" t="s">
+      <c r="B121" s="4" t="s">
         <v>317</v>
       </c>
       <c r="C121" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D121" t="s">
         <v>318</v>
       </c>
-      <c r="D121" t="s">
+    </row>
+    <row r="123" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B123" s="4" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="123" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B123" s="6" t="s">
+      <c r="C123" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="D123" t="s">
         <v>320</v>
       </c>
-      <c r="C123" s="1" t="s">
+    </row>
+    <row r="125" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B125" s="6"/>
+    </row>
+    <row r="127" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B127" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="D123" t="s">
+      <c r="C127" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D127" t="s">
         <v>322</v>
-      </c>
-    </row>
-    <row r="125" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B125" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="D125" t="s">
-        <v>324</v>
-      </c>
-      <c r="E125">
-        <v>82217957764</v>
-      </c>
-    </row>
-    <row r="127" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B127" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="D127" t="s">
-        <v>327</v>
       </c>
       <c r="E127">
         <v>85389213779</v>
       </c>
     </row>
     <row r="129" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B129" s="6" t="s">
-        <v>328</v>
+      <c r="B129" s="4" t="s">
+        <v>323</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>112</v>
       </c>
       <c r="D129" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="131" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B131" s="6" t="s">
-        <v>330</v>
+      <c r="B131" s="4" t="s">
+        <v>325</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>331</v>
+        <v>427</v>
       </c>
       <c r="D131" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
     </row>
     <row r="133" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B133" s="6" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="D133" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="135" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B135" s="6" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D135" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="137" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B137" s="6" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="D137" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="139" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B139" s="6" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="D139" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="E139">
         <v>82350736942</v>
@@ -3188,13 +3165,13 @@
     </row>
     <row r="144" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B144" s="4" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="D144" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="E144">
         <v>85348011491</v>
@@ -3202,79 +3179,79 @@
     </row>
     <row r="146" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B146" s="4" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="D146" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
     </row>
     <row r="148" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B148" s="4" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D148" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="150" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B150" s="4" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="D150" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
     </row>
     <row r="152" spans="2:5" ht="45" x14ac:dyDescent="0.25">
       <c r="B152" s="4" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="D152" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="154" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B154" s="4" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="D154" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="156" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B156" s="4" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="D156" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
     </row>
     <row r="158" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B158" s="4" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="D158" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E158">
         <v>81255092909</v>
@@ -3282,112 +3259,112 @@
     </row>
     <row r="160" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B160" s="4" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="D160" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="162" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B162" s="7" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="D162" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
     </row>
     <row r="164" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B164" s="6" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="D164" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="166" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B166" s="6" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="D166" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="168" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B168" s="6" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="D168" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="170" spans="2:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B170" s="6" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="D170" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
     </row>
     <row r="172" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B172" s="6" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="D172" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
     </row>
     <row r="174" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B174" s="2" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="D174" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="176" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B176" s="6" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="D176" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="178" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B178" s="6" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="D178" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="E178">
         <v>85389740433</v>
@@ -3395,35 +3372,35 @@
     </row>
     <row r="180" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B180" s="6" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="D180" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="182" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B182" s="6" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="C182" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D182" t="s">
         <v>410</v>
-      </c>
-      <c r="D182" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="184" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B184" s="6" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="D184" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="E184">
         <v>85250259035</v>
@@ -3431,13 +3408,13 @@
     </row>
     <row r="186" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B186" s="6" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="D186" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="E186">
         <v>82155111101</v>
@@ -3445,24 +3422,24 @@
     </row>
     <row r="188" spans="2:5" ht="45" x14ac:dyDescent="0.25">
       <c r="B188" s="6" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D188" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
     </row>
     <row r="190" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B190" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="C190" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="C190" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="D190" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="E190">
         <v>85654141138</v>

--- a/New folder (2)/kutai timur.xlsx
+++ b/New folder (2)/kutai timur.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jati\Documents\GitHub2\kutaitimur.github.io\New folder (2)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D45F9C-1B50-4AC7-AE62-3646E269028A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9388A951-2B95-4661-960F-900B61FD3C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="426">
   <si>
     <t>Indomaret AWS Sangatta</t>
   </si>
@@ -1009,18 +1009,12 @@
     <t>Subur Fruits</t>
   </si>
   <si>
-    <t>3VRW+MM8, Jl. Ahmad Yani, Marga Mulia, Kec. Kongbeng, Kabupaten Kutai Timur, Kalimantan Timur 75655</t>
-  </si>
-  <si>
     <t>1.0916865508333784, 116.89674982599873</t>
   </si>
   <si>
     <t>Kedai Sayur Kiki Mekar Jaya</t>
   </si>
   <si>
-    <t>3VRX+X36, Marga Mulia, Kec. Kongbeng, Kabupaten Kutai Timur, Kalimantan Timur 75655</t>
-  </si>
-  <si>
     <t>1.0924052522870187, 116.89765641264844</t>
   </si>
   <si>
@@ -1033,12 +1027,6 @@
     <t>1.092960341737123, 116.90095722128483</t>
   </si>
   <si>
-    <t>Kios dua putri</t>
-  </si>
-  <si>
-    <t>3WV4+5J2, Marga Mulia, Kec. Kongbeng, Kabupaten Kutai Timur, Kalimantan Timur 75655</t>
-  </si>
-  <si>
     <t>1.0929030812014808, 116.9065234000066</t>
   </si>
   <si>
@@ -1310,6 +1298,9 @@
   </si>
   <si>
     <t>Wanasari, Kec. Kongbeng, Kabupaten Kutai Timur, Kalimantan Timur 75655</t>
+  </si>
+  <si>
+    <t>Kios Dua Putri</t>
   </si>
 </sst>
 </file>
@@ -2147,13 +2138,13 @@
     </row>
     <row r="51" spans="2:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B51" s="4" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D51" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -2345,13 +2336,13 @@
     </row>
     <row r="27" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C27" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="D27" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -2676,7 +2667,7 @@
         <v>273</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="D50" t="s">
         <v>145</v>
@@ -2687,7 +2678,7 @@
         <v>154</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>155</v>
@@ -2869,7 +2860,7 @@
         <v>280</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D88" t="s">
         <v>281</v>
@@ -2880,7 +2871,7 @@
         <v>285</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D90" t="s">
         <v>286</v>
@@ -2891,7 +2882,7 @@
         <v>287</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D92" t="s">
         <v>288</v>
@@ -2902,7 +2893,7 @@
         <v>289</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D94" t="s">
         <v>290</v>
@@ -2927,7 +2918,7 @@
         <v>295</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="D99" t="s">
         <v>294</v>
@@ -2952,7 +2943,7 @@
         <v>299</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="D103" t="s">
         <v>300</v>
@@ -2963,7 +2954,7 @@
         <v>301</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D105" t="s">
         <v>302</v>
@@ -2974,7 +2965,7 @@
         <v>303</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D107" t="s">
         <v>304</v>
@@ -2988,7 +2979,7 @@
         <v>305</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="D109" t="s">
         <v>306</v>
@@ -3002,7 +2993,7 @@
         <v>307</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="D111" t="s">
         <v>308</v>
@@ -3013,7 +3004,7 @@
         <v>310</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="D113" t="s">
         <v>309</v>
@@ -3024,7 +3015,7 @@
         <v>311</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D115" t="s">
         <v>312</v>
@@ -3038,7 +3029,7 @@
         <v>313</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="D117" t="s">
         <v>314</v>
@@ -3049,7 +3040,7 @@
         <v>315</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="D119" t="s">
         <v>316</v>
@@ -3060,7 +3051,7 @@
         <v>317</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D121" t="s">
         <v>318</v>
@@ -3071,7 +3062,7 @@
         <v>319</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D123" t="s">
         <v>320</v>
@@ -3085,7 +3076,7 @@
         <v>321</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D127" t="s">
         <v>322</v>
@@ -3110,54 +3101,54 @@
         <v>325</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D131" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="133" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B133" s="6" t="s">
+      <c r="B133" s="4" t="s">
         <v>327</v>
       </c>
       <c r="C133" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="D133" t="s">
         <v>328</v>
       </c>
-      <c r="D133" t="s">
+    </row>
+    <row r="135" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B135" s="4" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="135" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B135" s="6" t="s">
+      <c r="C135" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D135" t="s">
         <v>330</v>
       </c>
-      <c r="C135" s="1" t="s">
+    </row>
+    <row r="137" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B137" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="D135" t="s">
+      <c r="C137" s="1" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="137" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B137" s="6" t="s">
+      <c r="D137" t="s">
         <v>333</v>
       </c>
-      <c r="C137" s="1" t="s">
+    </row>
+    <row r="139" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B139" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D139" t="s">
         <v>334</v>
-      </c>
-      <c r="D137" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="139" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B139" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="D139" t="s">
-        <v>338</v>
       </c>
       <c r="E139">
         <v>82350736942</v>
@@ -3165,13 +3156,13 @@
     </row>
     <row r="144" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B144" s="4" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D144" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E144">
         <v>85348011491</v>
@@ -3179,79 +3170,79 @@
     </row>
     <row r="146" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B146" s="4" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="D146" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="148" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B148" s="4" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D148" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="150" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B150" s="4" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D150" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="152" spans="2:5" ht="45" x14ac:dyDescent="0.25">
       <c r="B152" s="4" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="D152" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="154" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B154" s="4" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D154" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="156" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B156" s="4" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D156" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="158" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B158" s="4" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="D158" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E158">
         <v>81255092909</v>
@@ -3259,112 +3250,112 @@
     </row>
     <row r="160" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B160" s="4" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D160" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="162" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B162" s="7" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D162" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="164" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B164" s="6" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D164" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="166" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B166" s="6" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D166" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="168" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B168" s="6" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D168" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="170" spans="2:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B170" s="6" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D170" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="172" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B172" s="6" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D172" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="174" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B174" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D174" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="176" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B176" s="6" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="D176" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="178" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B178" s="6" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D178" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="E178">
         <v>85389740433</v>
@@ -3372,35 +3363,35 @@
     </row>
     <row r="180" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B180" s="6" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D180" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="182" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B182" s="6" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D182" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="184" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B184" s="6" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="D184" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="E184">
         <v>85250259035</v>
@@ -3408,13 +3399,13 @@
     </row>
     <row r="186" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B186" s="6" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="D186" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="E186">
         <v>82155111101</v>
@@ -3422,24 +3413,24 @@
     </row>
     <row r="188" spans="2:5" ht="45" x14ac:dyDescent="0.25">
       <c r="B188" s="6" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D188" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="190" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B190" s="6" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="D190" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E190">
         <v>85654141138</v>

--- a/New folder (2)/kutai timur.xlsx
+++ b/New folder (2)/kutai timur.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jati\Documents\GitHub2\kutaitimur.github.io\New folder (2)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9388A951-2B95-4661-960F-900B61FD3C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E6146F-F3FB-4A52-95B8-029C5BD37634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1123,9 +1123,6 @@
     <t>TOKO AFNAN</t>
   </si>
   <si>
-    <t>JPJ2+74, Muara Bengalon, Kec. Bengalon, Kabupaten Kutai Timur, Kalimantan Timur 75618</t>
-  </si>
-  <si>
     <t>0.6307266393515597, 117.70025909123304</t>
   </si>
   <si>
@@ -1150,9 +1147,6 @@
     <t>Toko ilma</t>
   </si>
   <si>
-    <t>PHWM+5CX, Sepaso Sel., Kec. Bengalon, Kabupaten Kutai Timur, Kalimantan Timur 75618</t>
-  </si>
-  <si>
     <t>0.7454860876767276, 117.58361094299775</t>
   </si>
   <si>
@@ -1301,6 +1295,12 @@
   </si>
   <si>
     <t>Kios Dua Putri</t>
+  </si>
+  <si>
+    <t>Muara Bengalon, Kec. Bengalon, Kabupaten Kutai Timur, Kalimantan Timur 75618</t>
+  </si>
+  <si>
+    <t>Sepaso Sel., Kec. Bengalon, Kabupaten Kutai Timur, Kalimantan Timur 75618</t>
   </si>
 </sst>
 </file>
@@ -2336,13 +2336,13 @@
     </row>
     <row r="27" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="C27" t="s">
+        <v>417</v>
+      </c>
+      <c r="D27" t="s">
         <v>418</v>
-      </c>
-      <c r="C27" t="s">
-        <v>419</v>
-      </c>
-      <c r="D27" t="s">
-        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -2667,7 +2667,7 @@
         <v>273</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D50" t="s">
         <v>145</v>
@@ -2678,7 +2678,7 @@
         <v>154</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>155</v>
@@ -2860,7 +2860,7 @@
         <v>280</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D88" t="s">
         <v>281</v>
@@ -2871,7 +2871,7 @@
         <v>285</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D90" t="s">
         <v>286</v>
@@ -2882,7 +2882,7 @@
         <v>287</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D92" t="s">
         <v>288</v>
@@ -2893,7 +2893,7 @@
         <v>289</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D94" t="s">
         <v>290</v>
@@ -2918,7 +2918,7 @@
         <v>295</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D99" t="s">
         <v>294</v>
@@ -2943,7 +2943,7 @@
         <v>299</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D103" t="s">
         <v>300</v>
@@ -2954,7 +2954,7 @@
         <v>301</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D105" t="s">
         <v>302</v>
@@ -2965,7 +2965,7 @@
         <v>303</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D107" t="s">
         <v>304</v>
@@ -2979,7 +2979,7 @@
         <v>305</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D109" t="s">
         <v>306</v>
@@ -2993,7 +2993,7 @@
         <v>307</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D111" t="s">
         <v>308</v>
@@ -3004,7 +3004,7 @@
         <v>310</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D113" t="s">
         <v>309</v>
@@ -3015,7 +3015,7 @@
         <v>311</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D115" t="s">
         <v>312</v>
@@ -3029,7 +3029,7 @@
         <v>313</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D117" t="s">
         <v>314</v>
@@ -3040,7 +3040,7 @@
         <v>315</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D119" t="s">
         <v>316</v>
@@ -3051,7 +3051,7 @@
         <v>317</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D121" t="s">
         <v>318</v>
@@ -3062,7 +3062,7 @@
         <v>319</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D123" t="s">
         <v>320</v>
@@ -3076,7 +3076,7 @@
         <v>321</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D127" t="s">
         <v>322</v>
@@ -3101,7 +3101,7 @@
         <v>325</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D131" t="s">
         <v>326</v>
@@ -3112,7 +3112,7 @@
         <v>327</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D133" t="s">
         <v>328</v>
@@ -3142,7 +3142,7 @@
     </row>
     <row r="139" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B139" s="4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>112</v>
@@ -3173,7 +3173,7 @@
         <v>341</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D146" t="s">
         <v>342</v>
@@ -3195,7 +3195,7 @@
         <v>346</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D150" t="s">
         <v>347</v>
@@ -3206,7 +3206,7 @@
         <v>348</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D152" t="s">
         <v>349</v>
@@ -3217,7 +3217,7 @@
         <v>350</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D154" t="s">
         <v>351</v>
@@ -3239,7 +3239,7 @@
         <v>355</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D158" t="s">
         <v>356</v>
@@ -3271,7 +3271,7 @@
       </c>
     </row>
     <row r="164" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B164" s="6" t="s">
+      <c r="B164" s="4" t="s">
         <v>362</v>
       </c>
       <c r="C164" s="1" t="s">
@@ -3282,80 +3282,80 @@
       </c>
     </row>
     <row r="166" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B166" s="6" t="s">
+      <c r="B166" s="4" t="s">
         <v>365</v>
       </c>
       <c r="C166" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="D166" t="s">
         <v>366</v>
       </c>
-      <c r="D166" t="s">
+    </row>
+    <row r="168" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B168" s="4" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="168" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B168" s="6" t="s">
+      <c r="C168" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="C168" s="1" t="s">
+      <c r="D168" t="s">
         <v>369</v>
       </c>
-      <c r="D168" t="s">
+    </row>
+    <row r="170" spans="2:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="B170" s="4" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="170" spans="2:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B170" s="6" t="s">
+      <c r="C170" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="C170" s="1" t="s">
+      <c r="D170" t="s">
         <v>372</v>
-      </c>
-      <c r="D170" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="172" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B172" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="D172" t="s">
         <v>374</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="D172" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="174" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B174" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C174" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="D174" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="176" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B176" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D176" t="s">
         <v>396</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="D176" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="178" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B178" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="D178" t="s">
         <v>399</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="D178" t="s">
-        <v>401</v>
       </c>
       <c r="E178">
         <v>85389740433</v>
@@ -3363,35 +3363,35 @@
     </row>
     <row r="180" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B180" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="D180" t="s">
         <v>402</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="D180" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="182" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B182" s="6" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D182" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="184" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B184" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D184" t="s">
         <v>407</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="D184" t="s">
-        <v>409</v>
       </c>
       <c r="E184">
         <v>85250259035</v>
@@ -3399,13 +3399,13 @@
     </row>
     <row r="186" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B186" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="D186" t="s">
         <v>410</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="D186" t="s">
-        <v>412</v>
       </c>
       <c r="E186">
         <v>82155111101</v>
@@ -3413,24 +3413,24 @@
     </row>
     <row r="188" spans="2:5" ht="45" x14ac:dyDescent="0.25">
       <c r="B188" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D188" t="s">
         <v>413</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="D188" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="190" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B190" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D190" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E190">
         <v>85654141138</v>

--- a/New folder (2)/kutai timur.xlsx
+++ b/New folder (2)/kutai timur.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jati\Documents\GitHub2\kutaitimur.github.io\New folder (2)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E6146F-F3FB-4A52-95B8-029C5BD37634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1798BBFF-D108-46FA-8729-777099023540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="425">
   <si>
     <t>Indomaret AWS Sangatta</t>
   </si>
@@ -1208,9 +1208,6 @@
   </si>
   <si>
     <t>CV. LANGGENG JAYA BERKAH</t>
-  </si>
-  <si>
-    <t>9GH8+R2R, Jl. Minyak, Sangkima, Kec. Sangatta Sel., Kabupaten Kutai Timur, Kalimantan Timur 75683</t>
   </si>
   <si>
     <t>0.38003909345959763, 117.5145104966527</t>
@@ -2336,13 +2333,13 @@
     </row>
     <row r="27" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="C27" t="s">
         <v>416</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>417</v>
-      </c>
-      <c r="D27" t="s">
-        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -3062,7 +3059,7 @@
         <v>319</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D123" t="s">
         <v>320</v>
@@ -3076,7 +3073,7 @@
         <v>321</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D127" t="s">
         <v>322</v>
@@ -3101,7 +3098,7 @@
         <v>325</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D131" t="s">
         <v>326</v>
@@ -3112,7 +3109,7 @@
         <v>327</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D133" t="s">
         <v>328</v>
@@ -3142,7 +3139,7 @@
     </row>
     <row r="139" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B139" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>112</v>
@@ -3239,7 +3236,7 @@
         <v>355</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D158" t="s">
         <v>356</v>
@@ -3286,7 +3283,7 @@
         <v>365</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D166" t="s">
         <v>366</v>
@@ -3315,11 +3312,11 @@
       </c>
     </row>
     <row r="172" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B172" s="6" t="s">
+      <c r="B172" s="4" t="s">
         <v>373</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D172" t="s">
         <v>374</v>
@@ -3337,25 +3334,25 @@
       </c>
     </row>
     <row r="176" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B176" s="6" t="s">
+      <c r="B176" s="4" t="s">
         <v>394</v>
       </c>
       <c r="C176" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D176" t="s">
         <v>395</v>
-      </c>
-      <c r="D176" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="178" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B178" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="C178" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C178" s="1" t="s">
+      <c r="D178" t="s">
         <v>398</v>
-      </c>
-      <c r="D178" t="s">
-        <v>399</v>
       </c>
       <c r="E178">
         <v>85389740433</v>
@@ -3363,35 +3360,35 @@
     </row>
     <row r="180" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B180" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="C180" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="C180" s="1" t="s">
+      <c r="D180" t="s">
         <v>401</v>
-      </c>
-      <c r="D180" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="182" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B182" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D182" t="s">
         <v>403</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="D182" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="184" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B184" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="C184" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C184" s="1" t="s">
+      <c r="D184" t="s">
         <v>406</v>
-      </c>
-      <c r="D184" t="s">
-        <v>407</v>
       </c>
       <c r="E184">
         <v>85250259035</v>
@@ -3399,13 +3396,13 @@
     </row>
     <row r="186" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B186" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="C186" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="C186" s="1" t="s">
+      <c r="D186" t="s">
         <v>409</v>
-      </c>
-      <c r="D186" t="s">
-        <v>410</v>
       </c>
       <c r="E186">
         <v>82155111101</v>
@@ -3413,24 +3410,24 @@
     </row>
     <row r="188" spans="2:5" ht="45" x14ac:dyDescent="0.25">
       <c r="B188" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="C188" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C188" s="1" t="s">
+      <c r="D188" t="s">
         <v>412</v>
-      </c>
-      <c r="D188" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="190" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B190" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D190" t="s">
         <v>414</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D190" t="s">
-        <v>415</v>
       </c>
       <c r="E190">
         <v>85654141138</v>

--- a/New folder (2)/kutai timur.xlsx
+++ b/New folder (2)/kutai timur.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jati\Documents\GitHub2\kutaitimur.github.io\New folder (2)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1798BBFF-D108-46FA-8729-777099023540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7751CD24-D347-4A55-991F-08B3C22B1994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="424">
   <si>
     <t>Indomaret AWS Sangatta</t>
   </si>
@@ -1225,9 +1225,6 @@
     <t>Toko Alfin (ATK, Bangunan, dan Pangkalan Gas)</t>
   </si>
   <si>
-    <t>9GJ7+MPM, RT.01/RW.Dusun Patra, Sangkima, Kec. Sangatta Sel., Kabupaten Kutai Timur, Kalimantan Timur 75683</t>
-  </si>
-  <si>
     <t>0.38171743856773815, 117.51430262294969</t>
   </si>
   <si>
@@ -1240,27 +1237,18 @@
     <t>Toko Nur Hadi</t>
   </si>
   <si>
-    <t>FGHV+338, Sangatta Sel., Kec. Sangatta Sel., Kabupaten Kutai Timur, Kalimantan Timur 75683</t>
-  </si>
-  <si>
     <t>0.477676307839722, 117.54270243372302</t>
   </si>
   <si>
     <t>Toko Bagus Cell</t>
   </si>
   <si>
-    <t>FGHR+6P7, Unnamed Road, Sangatta Sel., Kec. Sangatta Sel., Kabupaten Kutai Timur, Kalimantan Timur 75683</t>
-  </si>
-  <si>
     <t>0.47807017959383447, 117.54181102777927</t>
   </si>
   <si>
     <t>TOKO AWANG JAYA RAKA</t>
   </si>
   <si>
-    <t>Jl. Rosihan Achmad No.61, kampung tengah, Sangatta Sel., Kec. Sangatta Utara, Kabupaten Kutai Timur, Kalimantan Timur 75683</t>
-  </si>
-  <si>
     <t>0.480865294607064, 117.53891311765523</t>
   </si>
   <si>
@@ -1298,6 +1286,15 @@
   </si>
   <si>
     <t>Sepaso Sel., Kec. Bengalon, Kabupaten Kutai Timur, Kalimantan Timur 75618</t>
+  </si>
+  <si>
+    <t>RT.01/RW.Dusun Patra, Sangkima, Kec. Sangatta Sel., Kabupaten Kutai Timur, Kalimantan Timur 75683</t>
+  </si>
+  <si>
+    <t>Sangatta Sel., Kec. Sangatta Sel., Kabupaten Kutai Timur, Kalimantan Timur 75683</t>
+  </si>
+  <si>
+    <t>Jl. Rosihan Achmad No.61, Kampung Tengah, Sangatta Sel., Kec. Sangatta Utara, Kabupaten Kutai Timur, Kalimantan Timur 75683</t>
   </si>
 </sst>
 </file>
@@ -2333,13 +2330,13 @@
     </row>
     <row r="27" spans="2:4" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C27" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="D27" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -3059,7 +3056,7 @@
         <v>319</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="D123" t="s">
         <v>320</v>
@@ -3073,7 +3070,7 @@
         <v>321</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="D127" t="s">
         <v>322</v>
@@ -3098,7 +3095,7 @@
         <v>325</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="D131" t="s">
         <v>326</v>
@@ -3109,7 +3106,7 @@
         <v>327</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="D133" t="s">
         <v>328</v>
@@ -3139,7 +3136,7 @@
     </row>
     <row r="139" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B139" s="4" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>112</v>
@@ -3236,7 +3233,7 @@
         <v>355</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D158" t="s">
         <v>356</v>
@@ -3283,7 +3280,7 @@
         <v>365</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="D166" t="s">
         <v>366</v>
@@ -3316,7 +3313,7 @@
         <v>373</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="D172" t="s">
         <v>374</v>
@@ -3345,7 +3342,7 @@
       </c>
     </row>
     <row r="178" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B178" s="6" t="s">
+      <c r="B178" s="4" t="s">
         <v>396</v>
       </c>
       <c r="C178" s="1" t="s">
@@ -3359,75 +3356,75 @@
       </c>
     </row>
     <row r="180" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B180" s="6" t="s">
+      <c r="B180" s="4" t="s">
         <v>399</v>
       </c>
       <c r="C180" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D180" t="s">
         <v>400</v>
       </c>
-      <c r="D180" t="s">
+    </row>
+    <row r="182" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B182" s="4" t="s">
         <v>401</v>
-      </c>
-    </row>
-    <row r="182" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B182" s="6" t="s">
-        <v>402</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>397</v>
       </c>
       <c r="D182" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="184" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B184" s="4" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="184" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B184" s="6" t="s">
+      <c r="C184" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D184" t="s">
         <v>404</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="D184" t="s">
-        <v>406</v>
       </c>
       <c r="E184">
         <v>85250259035</v>
       </c>
     </row>
     <row r="186" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B186" s="6" t="s">
-        <v>407</v>
+      <c r="B186" s="4" t="s">
+        <v>405</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="D186" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E186">
         <v>82155111101</v>
       </c>
     </row>
     <row r="188" spans="2:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="B188" s="6" t="s">
+      <c r="B188" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="D188" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="190" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B190" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D190" t="s">
         <v>410</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="D188" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="190" spans="2:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B190" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="D190" t="s">
-        <v>414</v>
       </c>
       <c r="E190">
         <v>85654141138</v>

--- a/New folder (2)/kutai timur.xlsx
+++ b/New folder (2)/kutai timur.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jati\Documents\GitHub2\kutaitimur.github.io\New folder (2)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7751CD24-D347-4A55-991F-08B3C22B1994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51FFAD49-5AA7-42E6-B3CF-482822A8D325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="470">
   <si>
     <t>Indomaret AWS Sangatta</t>
   </si>
@@ -1295,13 +1295,151 @@
   </si>
   <si>
     <t>Jl. Rosihan Achmad No.61, Kampung Tengah, Sangatta Sel., Kec. Sangatta Utara, Kabupaten Kutai Timur, Kalimantan Timur 75683</t>
+  </si>
+  <si>
+    <t>SRC Maju Jaya</t>
+  </si>
+  <si>
+    <t>1.044440201057999, 116.84564514101645</t>
+  </si>
+  <si>
+    <t>1.0942775147487422, 116.92277897826506</t>
+  </si>
+  <si>
+    <t>Jl. Samarinda - Berau No.rt 11, Makmur Jaya, Kec. Kongbeng, Kabupaten Kutai Timur, Kalimantan Timur 75657</t>
+  </si>
+  <si>
+    <t>1.127440181124076, 116.93752417407914</t>
+  </si>
+  <si>
+    <t>Toko Salmah</t>
+  </si>
+  <si>
+    <t>1.128399098595896, 116.93955792086618</t>
+  </si>
+  <si>
+    <t>1.130255817666981, 116.9441325090366</t>
+  </si>
+  <si>
+    <t>RAQILRARAJAYA</t>
+  </si>
+  <si>
+    <t>1.1321357441557658, 116.94751148269404</t>
+  </si>
+  <si>
+    <t>ECHA BARATA</t>
+  </si>
+  <si>
+    <t>Jl. Samarinda - Berau, Makmur Jaya, simpang matra sawit, Kabupaten Kutai Timur, Kalimantan Timur 75656</t>
+  </si>
+  <si>
+    <t>1.141229209771072, 116.95045244763</t>
+  </si>
+  <si>
+    <t>Toko Amar Cell</t>
+  </si>
+  <si>
+    <t>RT.7, Miau Baru, Kec. Kongbeng, Kabupaten Kutai Timur, Kalimantan Timur 75655</t>
+  </si>
+  <si>
+    <t>1.196701348625749, 116.94718490157324</t>
+  </si>
+  <si>
+    <t>Toko Fitrah</t>
+  </si>
+  <si>
+    <t>0.8346272815948741, 118.01441377975422</t>
+  </si>
+  <si>
+    <t>TOKO ALISA NADA</t>
+  </si>
+  <si>
+    <t>0.8083997041967709, 117.96003282338883</t>
+  </si>
+  <si>
+    <t>Toko Putri</t>
+  </si>
+  <si>
+    <t>0.898261159673172, 118.20626138408474</t>
+  </si>
+  <si>
+    <t>Toko Tasya</t>
+  </si>
+  <si>
+    <t>0.8968185690489109, 118.20393260904778</t>
+  </si>
+  <si>
+    <t>0.9004410281663519, 118.20875320165956</t>
+  </si>
+  <si>
+    <t>0.9066891776849634, 118.21095730692272</t>
+  </si>
+  <si>
+    <t>Kios Ikan Wisty Andira</t>
+  </si>
+  <si>
+    <t>0.9051942112547684, 118.21003110996368</t>
+  </si>
+  <si>
+    <t>Kios Sayur Al Farizi</t>
+  </si>
+  <si>
+    <t>0.9052364507737293, 118.210124316728</t>
+  </si>
+  <si>
+    <t>Kios Ikan Jaya Abadi</t>
+  </si>
+  <si>
+    <t>0.9081622126624113, 118.21124121250104</t>
+  </si>
+  <si>
+    <t>Agen Telur Blitar Berkah Bersama</t>
+  </si>
+  <si>
+    <t>Bumi Jaya, Kec. Kaubun, Kabupaten Kutai Timur, Kalimantan Timur</t>
+  </si>
+  <si>
+    <t>1.0657866740964672, 117.85343907012458</t>
+  </si>
+  <si>
+    <t>1.0826070914550427, 117.85419159866157</t>
+  </si>
+  <si>
+    <t>Toko Sayur Murah</t>
+  </si>
+  <si>
+    <t>Toko Yusak Jalan Poros</t>
+  </si>
+  <si>
+    <t>Cahaya Belawa</t>
+  </si>
+  <si>
+    <t>Jalan Ngelawan RT 02 Bual-Bual, Kerayaan, Kec. Sangkulirang, Kabupaten Kutai Timur, Kalimantan Timur 75684</t>
+  </si>
+  <si>
+    <t>Bumi Sejahtera, Kec. Kaliorang, Kabupaten Kutai Timur, Kalimantan Timur 75684</t>
+  </si>
+  <si>
+    <t>Susuk Luar, Kec. Sandaran, Kabupaten Kutai Timur, Kalimantan Timur 75685</t>
+  </si>
+  <si>
+    <t>Toko Fajar</t>
+  </si>
+  <si>
+    <t>Ayam Potong Delta Sangkulirang</t>
+  </si>
+  <si>
+    <t>Toko Dua Putra</t>
+  </si>
+  <si>
+    <t>Bumi Etam, Kec. Kaubun, Kabupaten Kutai Timur, Kalimantan Timur 75619</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1318,6 +1456,11 @@
       <family val="2"/>
       <charset val="1"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Roboto"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1352,7 +1495,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1370,6 +1513,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2346,7 +2495,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:E190"/>
+  <dimension ref="B1:E240"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.85546875" customWidth="1"/>
@@ -3428,6 +3577,257 @@
       </c>
       <c r="E190">
         <v>85654141138</v>
+      </c>
+    </row>
+    <row r="192" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B192" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D192" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="194" spans="2:5" ht="92.25" x14ac:dyDescent="0.25">
+      <c r="B194" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D194" t="s">
+        <v>426</v>
+      </c>
+      <c r="E194">
+        <v>81258021863</v>
+      </c>
+    </row>
+    <row r="196" spans="2:5" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="B196" s="8"/>
+    </row>
+    <row r="198" spans="2:5" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="B198" s="8"/>
+    </row>
+    <row r="200" spans="2:5" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="B200" s="8"/>
+    </row>
+    <row r="202" spans="2:5" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="B202" s="8"/>
+    </row>
+    <row r="204" spans="2:5" ht="123" x14ac:dyDescent="0.25">
+      <c r="B204" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="D204" t="s">
+        <v>428</v>
+      </c>
+      <c r="E204">
+        <v>81254871468</v>
+      </c>
+    </row>
+    <row r="206" spans="2:5" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="B206" s="8"/>
+    </row>
+    <row r="208" spans="2:5" ht="61.5" x14ac:dyDescent="0.25">
+      <c r="B208" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D208" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="210" spans="2:5" ht="61.5" x14ac:dyDescent="0.25">
+      <c r="B210" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D210" t="s">
+        <v>431</v>
+      </c>
+      <c r="E210">
+        <v>81352698561</v>
+      </c>
+    </row>
+    <row r="212" spans="2:5" ht="61.5" x14ac:dyDescent="0.25">
+      <c r="B212" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D212" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="214" spans="2:5" ht="30.75" x14ac:dyDescent="0.25">
+      <c r="B214" s="8"/>
+    </row>
+    <row r="216" spans="2:5" ht="61.5" x14ac:dyDescent="0.25">
+      <c r="B216" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D216" t="s">
+        <v>436</v>
+      </c>
+      <c r="E216">
+        <v>85386472133</v>
+      </c>
+    </row>
+    <row r="218" spans="2:5" ht="92.25" x14ac:dyDescent="0.25">
+      <c r="B218" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="D218" t="s">
+        <v>439</v>
+      </c>
+      <c r="E218">
+        <v>85787337044</v>
+      </c>
+    </row>
+    <row r="220" spans="2:5" ht="61.5" x14ac:dyDescent="0.25">
+      <c r="B220" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="D220" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="222" spans="2:5" ht="92.25" x14ac:dyDescent="0.25">
+      <c r="B222" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="D222" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="224" spans="2:5" ht="61.5" x14ac:dyDescent="0.25">
+      <c r="B224" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D224" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="226" spans="2:5" ht="61.5" x14ac:dyDescent="0.25">
+      <c r="B226" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D226" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="228" spans="2:5" ht="61.5" x14ac:dyDescent="0.25">
+      <c r="B228" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D228" t="s">
+        <v>448</v>
+      </c>
+      <c r="E228">
+        <v>8565155964</v>
+      </c>
+    </row>
+    <row r="230" spans="2:5" ht="153.75" x14ac:dyDescent="0.25">
+      <c r="B230" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D230" t="s">
+        <v>449</v>
+      </c>
+      <c r="E230">
+        <v>85752018758</v>
+      </c>
+    </row>
+    <row r="232" spans="2:5" ht="92.25" x14ac:dyDescent="0.25">
+      <c r="B232" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D232" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="234" spans="2:5" ht="92.25" x14ac:dyDescent="0.25">
+      <c r="B234" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D234" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="236" spans="2:5" ht="92.25" x14ac:dyDescent="0.25">
+      <c r="B236" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D236" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="238" spans="2:5" ht="153.75" x14ac:dyDescent="0.25">
+      <c r="B238" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="D238" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="240" spans="2:5" ht="61.5" x14ac:dyDescent="0.25">
+      <c r="B240" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="D240" t="s">
+        <v>459</v>
+      </c>
+      <c r="E240">
+        <v>82255331770</v>
       </c>
     </row>
   </sheetData>
